--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.64391</v>
+        <v>17.10346</v>
       </c>
       <c r="D2" t="n">
-        <v>16.98833</v>
+        <v>16.85653</v>
       </c>
       <c r="E2" t="n">
-        <v>16.97593</v>
+        <v>17.08345</v>
       </c>
       <c r="F2" t="n">
-        <v>42.75181</v>
+        <v>42.82408</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05131</v>
+        <v>0.05017</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82342</v>
+        <v>1.8456</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.71932</v>
+        <v>17.13083</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73879</v>
+        <v>16.81065</v>
       </c>
       <c r="E3" t="n">
-        <v>17.04919</v>
+        <v>16.93851</v>
       </c>
       <c r="F3" t="n">
-        <v>43.14568</v>
+        <v>43.24721</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05083</v>
+        <v>0.05191</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84054</v>
+        <v>1.84269</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.99402</v>
+        <v>16.90038</v>
       </c>
       <c r="D4" t="n">
-        <v>16.67631</v>
+        <v>16.86653</v>
       </c>
       <c r="E4" t="n">
-        <v>16.78738</v>
+        <v>16.88592</v>
       </c>
       <c r="F4" t="n">
-        <v>43.47309</v>
+        <v>42.34479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0521</v>
+        <v>0.05146</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83658</v>
+        <v>1.82697</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.65599</v>
+        <v>17.24191</v>
       </c>
       <c r="D6" t="n">
-        <v>16.21901</v>
+        <v>16.48499</v>
       </c>
       <c r="E6" t="n">
-        <v>16.76034</v>
+        <v>16.58072</v>
       </c>
       <c r="F6" t="n">
-        <v>21.68513</v>
+        <v>22.36649</v>
       </c>
       <c r="G6" t="n">
-        <v>34.87314</v>
+        <v>34.97229</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.83175</v>
+        <v>17.01355</v>
       </c>
       <c r="D7" t="n">
-        <v>15.92196</v>
+        <v>15.96526</v>
       </c>
       <c r="E7" t="n">
-        <v>16.45468</v>
+        <v>16.7096</v>
       </c>
       <c r="F7" t="n">
-        <v>22.06182</v>
+        <v>21.86888</v>
       </c>
       <c r="G7" t="n">
-        <v>34.24768</v>
+        <v>34.40062</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.9787</v>
+        <v>17.00374</v>
       </c>
       <c r="D8" t="n">
-        <v>16.08035</v>
+        <v>16.23742</v>
       </c>
       <c r="E8" t="n">
-        <v>16.73743</v>
+        <v>16.35548</v>
       </c>
       <c r="F8" t="n">
-        <v>22.19769</v>
+        <v>22.06382</v>
       </c>
       <c r="G8" t="n">
-        <v>34.25909</v>
+        <v>34.88871</v>
       </c>
     </row>
   </sheetData>
